--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.47249966001657</v>
+        <v>9.826781194752693</v>
       </c>
       <c r="D2" t="n">
-        <v>60.43542901496701</v>
+        <v>9.820757214932138</v>
       </c>
       <c r="E2" t="n">
-        <v>10.23053420791314</v>
+        <v>1.662461808785885</v>
       </c>
       <c r="F2" t="n">
-        <v>13.16658453383753</v>
+        <v>2.139569986748598</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.85560370275342</v>
+        <v>6.151535601697431</v>
       </c>
       <c r="D3" t="n">
-        <v>37.95923296274684</v>
+        <v>6.168375356446361</v>
       </c>
       <c r="E3" t="n">
-        <v>10.23053420791314</v>
+        <v>1.662461808785885</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16658453383753</v>
+        <v>2.139569986748598</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.1353739549773</v>
+        <v>6.034498267683812</v>
       </c>
       <c r="D4" t="n">
-        <v>37.00021694677632</v>
+        <v>6.012535253851152</v>
       </c>
       <c r="E4" t="n">
-        <v>10.23053420791314</v>
+        <v>1.662461808785885</v>
       </c>
       <c r="F4" t="n">
-        <v>13.16658453383753</v>
+        <v>2.139569986748598</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.56611202704985</v>
+        <v>8.866993204395602</v>
       </c>
       <c r="D5" t="n">
-        <v>23.78788807406891</v>
+        <v>3.865531812036198</v>
       </c>
       <c r="E5" t="n">
-        <v>10.23053420791314</v>
+        <v>1.662461808785885</v>
       </c>
       <c r="F5" t="n">
-        <v>13.16658453383753</v>
+        <v>2.139569986748598</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
